--- a/xls/square_16_tri3_24.xlsx
+++ b/xls/square_16_tri3_24.xlsx
@@ -482,13 +482,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-2.1720874481317405</v>
+        <v>-2.1720870786448265</v>
       </c>
       <c r="J24">
-        <v>-1.7569996464490463</v>
+        <v>-1.7569997498860488</v>
       </c>
       <c r="K24">
-        <v>2.7380940622836967</v>
+        <v>2.7380941992559724</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -517,13 +517,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-1.2848534574878236</v>
+        <v>-1.2848535499600455</v>
       </c>
       <c r="J25">
-        <v>-1.0677477317168513</v>
+        <v>-1.0677477765459737</v>
       </c>
       <c r="K25">
-        <v>3.5973662645706104</v>
+        <v>3.5973662735527383</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -552,13 +552,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.6298011408187838</v>
+        <v>-0.6298011418478039</v>
       </c>
       <c r="J26">
-        <v>-0.5264535237167329</v>
+        <v>-0.5264535248722189</v>
       </c>
       <c r="K26">
-        <v>3.8813800997538124</v>
+        <v>3.8813801006961204</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -587,13 +587,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-0.4839907577574603</v>
+        <v>-0.4839907650124831</v>
       </c>
       <c r="J27">
-        <v>-0.42279728009765727</v>
+        <v>-0.42279728526748717</v>
       </c>
       <c r="K27">
-        <v>3.913475117590202</v>
+        <v>3.913475120725106</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -622,13 +622,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-0.004237045085331175</v>
+        <v>-0.00423704510520455</v>
       </c>
       <c r="J28">
-        <v>-0.0033306188950215664</v>
+        <v>-0.003330618906681271</v>
       </c>
       <c r="K28">
-        <v>3.1199135338433868</v>
+        <v>3.1199135340241786</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -657,13 +657,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-0.0020604969101946256</v>
+        <v>-0.0020604969102320744</v>
       </c>
       <c r="J29">
-        <v>-0.001682765485589972</v>
+        <v>-0.0016827654857586101</v>
       </c>
       <c r="K29">
-        <v>2.9856116679197444</v>
+        <v>2.9856116679933136</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -692,13 +692,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-0.0006952871329288109</v>
+        <v>-0.0006952871328991103</v>
       </c>
       <c r="J30">
-        <v>-0.0005212920347106466</v>
+        <v>-0.0005212920346810545</v>
       </c>
       <c r="K30">
-        <v>2.7016956307218054</v>
+        <v>2.701695630722218</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -727,13 +727,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-0.01284763142094661</v>
+        <v>-0.01284763137780717</v>
       </c>
       <c r="J31">
-        <v>-0.009216000287849942</v>
+        <v>-0.009216000258489706</v>
       </c>
       <c r="K31">
-        <v>3.161087183737094</v>
+        <v>3.161087183165191</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -762,13 +762,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-0.00033784326460381976</v>
+        <v>-0.00033784326443290444</v>
       </c>
       <c r="J32">
-        <v>-0.00027315011707330407</v>
+        <v>-0.0002731501169628191</v>
       </c>
       <c r="K32">
-        <v>2.593677355115389</v>
+        <v>2.5936773548229124</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_24.xlsx
+++ b/xls/square_16_tri3_24.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>625</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>289</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>529</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>2904</v>
+      </c>
+      <c r="I22">
+        <v>1.3900785195540701</v>
+      </c>
+      <c r="J22">
+        <v>-1.6174695236449392</v>
+      </c>
+      <c r="K22">
+        <v>2.4108059143093183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>625</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>289</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>576</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23">
+        <v>3174</v>
+      </c>
+      <c r="I23">
+        <v>-1.5503343027376473</v>
+      </c>
+      <c r="J23">
+        <v>-1.9533579299943404</v>
+      </c>
+      <c r="K23">
+        <v>2.6686571836079134</v>
+      </c>
+    </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
         <v>11</v>
